--- a/astro-site/public/dl/kit-tareas-sushi-bar/BONUS-01-briefing-servicio.xlsx
+++ b/astro-site/public/dl/kit-tareas-sushi-bar/BONUS-01-briefing-servicio.xlsx
@@ -64,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -77,11 +77,20 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,6 +99,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,14 +464,15 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -469,6 +480,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -476,6 +488,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -504,6 +517,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -511,6 +525,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -539,6 +554,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -546,8 +562,25 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-sushi-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -556,9 +589,9 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C37"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -566,6 +599,7 @@
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="4" t="inlineStr">
         <is>
@@ -573,6 +607,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -609,6 +644,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -622,6 +658,7 @@
           <t>Pieza 1: __________ (origen: __________ kg: ____)</t>
         </is>
       </c>
+      <c r="C9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
@@ -629,6 +666,7 @@
           <t>Pieza 2: __________ (origen: __________ kg: ____)</t>
         </is>
       </c>
+      <c r="C10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="7" t="inlineStr">
@@ -636,6 +674,7 @@
           <t>Pieza 3: __________ (origen: __________ kg: ____)</t>
         </is>
       </c>
+      <c r="C11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
@@ -643,6 +682,7 @@
           <t>Pieza 4: __________ (origen: __________ kg: ____)</t>
         </is>
       </c>
+      <c r="C12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="7" t="inlineStr">
@@ -650,7 +690,9 @@
           <t>Especial del dia: __________</t>
         </is>
       </c>
-    </row>
+      <c r="C13" s="8" t="n"/>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -664,6 +706,7 @@
           <t>Reserva mesa ___: alergeno __________ (alternativa: __________)</t>
         </is>
       </c>
+      <c r="C16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
@@ -671,6 +714,7 @@
           <t>Reserva mesa ___: alergeno __________ (alternativa: __________)</t>
         </is>
       </c>
+      <c r="C17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
@@ -678,7 +722,9 @@
           <t>Nota general: __________</t>
         </is>
       </c>
-    </row>
+      <c r="C18" s="8" t="n"/>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
@@ -692,6 +738,7 @@
           <t>☐ Omakase barra: ___ pax a las ___:___ (preferencias: __________)</t>
         </is>
       </c>
+      <c r="C21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
@@ -699,6 +746,7 @@
           <t>☐ VIP mesa ___: ___ pax (nombre: __________ nota: __________)</t>
         </is>
       </c>
+      <c r="C22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
@@ -706,7 +754,9 @@
           <t>☐ Grupo ___pax mesa ___ a las ___:___</t>
         </is>
       </c>
-    </row>
+      <c r="C23" s="8" t="n"/>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
@@ -720,6 +770,7 @@
           <t>☐ Arroz sushi: ___kg preparados (suficiente: ☐ Si ☐ No)</t>
         </is>
       </c>
+      <c r="C26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="7" t="inlineStr">
@@ -727,6 +778,7 @@
           <t>☐ Nori: ___hojas (suficiente: ☐ Si ☐ No)</t>
         </is>
       </c>
+      <c r="C27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="7" t="inlineStr">
@@ -734,7 +786,9 @@
           <t>☐ Producto bajo stock: __________</t>
         </is>
       </c>
-    </row>
+      <c r="C28" s="8" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
@@ -748,6 +802,7 @@
           <t>Venta objetivo: _____ EUR</t>
         </is>
       </c>
+      <c r="C31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
@@ -755,6 +810,7 @@
           <t>Plato a empujar: __________</t>
         </is>
       </c>
+      <c r="C32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="7" t="inlineStr">
@@ -762,6 +818,7 @@
           <t>Sake/bebida a recomendar: __________</t>
         </is>
       </c>
+      <c r="C33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
@@ -769,7 +826,10 @@
           <t>Nota equipo: __________</t>
         </is>
       </c>
-    </row>
+      <c r="C34" s="8" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="2" t="inlineStr">
         <is>
@@ -779,26 +839,35 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B26:C26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>